--- a/src/attributions/attributions_ig_traj_498.xlsx
+++ b/src/attributions/attributions_ig_traj_498.xlsx
@@ -999,106 +999,106 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.005130496560918854</v>
+        <v>0.08180619508242522</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.02392885496758202</v>
+        <v>-0.06966416936769898</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.01693560061416057</v>
+        <v>-0.01689460352763158</v>
       </c>
       <c r="F2" t="n">
         <v>-0</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02471286464988766</v>
+        <v>0.1076614149606484</v>
       </c>
       <c r="K2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.004547601632370699</v>
+        <v>-0.2665002905176892</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02502063099885841</v>
+        <v>-0.02229189801986751</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P2" t="n">
         <v>-0</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.02766699180611887</v>
+        <v>0.06523898917771898</v>
       </c>
       <c r="T2" t="n">
         <v>-0</v>
       </c>
       <c r="U2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.05419437097972913</v>
+        <v>-0.006792529185243611</v>
       </c>
       <c r="W2" t="n">
-        <v>0.02599247979354504</v>
+        <v>0.1019388321749372</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.004743365091757061</v>
+        <v>-0.1197751438091222</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>-0.02707591191183536</v>
+        <v>0.001208917980645753</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.01709765687544249</v>
+        <v>0.1115829019469602</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>0</v>
@@ -1107,46 +1107,46 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.01784621566429674</v>
+        <v>-0.01585388062436088</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.002509656631344049</v>
+        <v>-0.01391789697518292</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.0591894262847708</v>
+        <v>0.08606597306684892</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.02245941889391236</v>
+        <v>-0.0151772353709747</v>
       </c>
       <c r="AU2" t="n">
         <v>0</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.03997207371561685</v>
+        <v>-0.1628732070325098</v>
       </c>
       <c r="AX2" t="n">
-        <v>-0.0222455408604398</v>
+        <v>-0.06493394482683863</v>
       </c>
       <c r="AY2" t="n">
         <v>-0</v>
@@ -1158,157 +1158,157 @@
         <v>0</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.02500263180353006</v>
+        <v>0.2484496395924873</v>
       </c>
       <c r="BD2" t="n">
         <v>0</v>
       </c>
       <c r="BE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.002168975133050314</v>
+        <v>0.1900924079345488</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.01063924078124795</v>
+        <v>0.1162872344726842</v>
       </c>
       <c r="BH2" t="n">
         <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.02326066322100957</v>
+        <v>-0.09635167323801712</v>
       </c>
       <c r="BM2" t="n">
         <v>0</v>
       </c>
       <c r="BN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.03178992770114826</v>
+        <v>0.07933840625463612</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.03817303067736682</v>
+        <v>-0.3797197699995991</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
       </c>
       <c r="BS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT2" t="n">
         <v>0</v>
       </c>
       <c r="BU2" t="n">
-        <v>-0.001857381766410295</v>
+        <v>-0.1435450796178133</v>
       </c>
       <c r="BV2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.01031704585172784</v>
+        <v>-0.3916789228249125</v>
       </c>
       <c r="BY2" t="n">
-        <v>-0.02132798982982983</v>
+        <v>-0.07666222198327177</v>
       </c>
       <c r="BZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="n">
         <v>0</v>
       </c>
       <c r="CC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0.007239308633253068</v>
+        <v>-0.1732429299268234</v>
       </c>
       <c r="CE2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.001301096967254109</v>
+        <v>0.2347897749485185</v>
       </c>
       <c r="CH2" t="n">
-        <v>0.01597316963689811</v>
+        <v>-0.02096170369514327</v>
       </c>
       <c r="CI2" t="n">
         <v>0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM2" t="n">
-        <v>-0.004172243429578691</v>
+        <v>0.009316888008131236</v>
       </c>
       <c r="CN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>-0.004981208171710785</v>
+        <v>0.2045244793011354</v>
       </c>
       <c r="CQ2" t="n">
-        <v>-0.01577156610364081</v>
+        <v>-0.1365389903829116</v>
       </c>
       <c r="CR2" t="n">
         <v>-0</v>
       </c>
       <c r="CS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
         <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>-0.00217257729493647</v>
+        <v>-0.2056382773864641</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.02182022279621677</v>
+        <v>0.2226105506470811</v>
       </c>
       <c r="CZ2" t="n">
-        <v>0.02569762313996425</v>
+        <v>0.02636915294041079</v>
       </c>
       <c r="DA2" t="n">
         <v>-0</v>
@@ -1317,13 +1317,13 @@
         <v>-0</v>
       </c>
       <c r="DC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD2" t="n">
         <v>-0</v>
       </c>
       <c r="DE2" t="n">
-        <v>-0.0002172611616025855</v>
+        <v>-0.03360667542425443</v>
       </c>
       <c r="DF2" t="n">
         <v>0</v>
@@ -1332,40 +1332,40 @@
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.08175342688176625</v>
+        <v>0.03800350770397942</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.05464954313494159</v>
+        <v>0.07784578992077129</v>
       </c>
       <c r="DJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
         <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN2" t="n">
-        <v>-0.01734652580522425</v>
+        <v>0.3492486282231088</v>
       </c>
       <c r="DO2" t="n">
         <v>-0</v>
       </c>
       <c r="DP2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>0.0114803559676882</v>
+        <v>0.02283808356363147</v>
       </c>
       <c r="DR2" t="n">
-        <v>0.1013287922281259</v>
+        <v>-0.1268152894021703</v>
       </c>
       <c r="DS2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
@@ -1377,25 +1377,25 @@
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0.01179741443645917</v>
+        <v>0.1359540611670603</v>
       </c>
       <c r="DX2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>-0.01433721291011771</v>
+        <v>-0.0436311433484231</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.02473195073079327</v>
+        <v>0.06328403603337394</v>
       </c>
       <c r="EB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED2" t="n">
         <v>0</v>
@@ -1404,19 +1404,19 @@
         <v>-0</v>
       </c>
       <c r="EF2" t="n">
-        <v>-0.01408018348142348</v>
+        <v>-0.2494162082746147</v>
       </c>
       <c r="EG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.0365070358046652</v>
+        <v>0.175799644224123</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.07043197269217763</v>
+        <v>0.07359353431649422</v>
       </c>
       <c r="EK2" t="n">
         <v>0</v>
@@ -1428,22 +1428,22 @@
         <v>0</v>
       </c>
       <c r="EN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO2" t="n">
-        <v>-0.01767988419955132</v>
+        <v>0.09061814911595152</v>
       </c>
       <c r="EP2" t="n">
         <v>-0</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.01408851028855623</v>
+        <v>0.2015936064103007</v>
       </c>
       <c r="ES2" t="n">
-        <v>0.04907402152391164</v>
+        <v>-0.1930820377797047</v>
       </c>
       <c r="ET2" t="n">
         <v>0</v>
@@ -1452,25 +1452,25 @@
         <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
       </c>
       <c r="EX2" t="n">
-        <v>-0.00326685600030628</v>
+        <v>-0.1540090273701296</v>
       </c>
       <c r="EY2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EZ2" t="n">
         <v>0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.01708878651669269</v>
+        <v>0.2807850755386338</v>
       </c>
       <c r="FB2" t="n">
-        <v>0.02962248912172181</v>
+        <v>0.02452974151785485</v>
       </c>
       <c r="FC2" t="n">
         <v>0</v>
@@ -1479,13 +1479,13 @@
         <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG2" t="n">
-        <v>0.01353753197573294</v>
+        <v>-0.1219873772984599</v>
       </c>
       <c r="FH2" t="n">
         <v>0</v>
@@ -1494,52 +1494,52 @@
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>0.0473094570095499</v>
+        <v>0.2983625186517619</v>
       </c>
       <c r="FK2" t="n">
-        <v>0.07124980721699638</v>
+        <v>-0.08674474434464556</v>
       </c>
       <c r="FL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM2" t="n">
         <v>-0</v>
       </c>
       <c r="FN2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO2" t="n">
         <v>-0</v>
       </c>
       <c r="FP2" t="n">
-        <v>-0.01169197431578245</v>
+        <v>-0.05717055511190823</v>
       </c>
       <c r="FQ2" t="n">
         <v>0</v>
       </c>
       <c r="FR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS2" t="n">
-        <v>-0.009271809757468087</v>
+        <v>0.4363379725507767</v>
       </c>
       <c r="FT2" t="n">
-        <v>0.08485382841411168</v>
+        <v>-0.3356754405815399</v>
       </c>
       <c r="FU2" t="n">
         <v>0</v>
       </c>
       <c r="FV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW2" t="n">
         <v>0</v>
       </c>
       <c r="FX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0.0007367975867645503</v>
+        <v>-0.1601703569057064</v>
       </c>
       <c r="FZ2" t="n">
         <v>0</v>
@@ -1548,13 +1548,13 @@
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>0.03456136806104576</v>
+        <v>0.2875343514167126</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
@@ -1571,19 +1571,19 @@
         <v>0</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.01802642255756185</v>
+        <v>-0.01119813874327076</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00137538753950138</v>
+        <v>-0.0001127699759848379</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5052551783512984</v>
+        <v>0.2174316366072572</v>
       </c>
       <c r="G3" t="n">
         <v>-0</v>
@@ -1592,10 +1592,10 @@
         <v>0</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
         <v>0</v>
@@ -1604,13 +1604,13 @@
         <v>-0</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0303317485894369</v>
+        <v>-0.03411606878955065</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.02436577158335003</v>
+        <v>-0.01046818517433169</v>
       </c>
       <c r="O3" t="n">
-        <v>0.3482606298072715</v>
+        <v>0.2716040404400336</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -1625,19 +1625,19 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>-0</v>
       </c>
       <c r="V3" t="n">
-        <v>0.01663914243282382</v>
+        <v>-0.0251684393647319</v>
       </c>
       <c r="W3" t="n">
-        <v>0.07818631825847189</v>
+        <v>0.01440226552087308</v>
       </c>
       <c r="X3" t="n">
-        <v>0.04737148275777644</v>
+        <v>0.01992243840682905</v>
       </c>
       <c r="Y3" t="n">
         <v>-0</v>
@@ -1652,22 +1652,22 @@
         <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE3" t="n">
-        <v>-0.02801164544941828</v>
+        <v>0.06081320220538571</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.02602505742690114</v>
+        <v>0.009160569141708517</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.02708899519688088</v>
+        <v>0.06644746459500875</v>
       </c>
       <c r="AH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>0</v>
@@ -1682,19 +1682,19 @@
         <v>0</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN3" t="n">
-        <v>-0.02702469349752857</v>
+        <v>-0.05991325199359206</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.0594813019651976</v>
+        <v>-0.04449568718485541</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.04579260220400171</v>
+        <v>0.05422422826157761</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR3" t="n">
         <v>0</v>
@@ -1703,49 +1703,49 @@
         <v>0</v>
       </c>
       <c r="AT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0.02005802770442524</v>
+        <v>-0.01886686426391277</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.04886987481839743</v>
+        <v>-0.05908324039709852</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.328190777470861</v>
+        <v>0.1938289001179573</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB3" t="n">
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BE3" t="n">
         <v>-0</v>
       </c>
       <c r="BF3" t="n">
-        <v>-0.01604642426108615</v>
+        <v>0.04521316104073924</v>
       </c>
       <c r="BG3" t="n">
-        <v>-0.00488960269155806</v>
+        <v>0.02053977810579325</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.08156072267757562</v>
+        <v>-0.03618036284276929</v>
       </c>
       <c r="BI3" t="n">
         <v>-0</v>
@@ -1766,40 +1766,40 @@
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.01078948871334732</v>
+        <v>-0.05684151994203138</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.02224153603180841</v>
+        <v>-0.03473911197051025</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.04228142164201944</v>
+        <v>0.01354402259730029</v>
       </c>
       <c r="BR3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>-0</v>
       </c>
       <c r="BU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX3" t="n">
-        <v>-0.02173066233972291</v>
+        <v>-0.118975622033987</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.03998230953093256</v>
+        <v>-0.01886736156762754</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.1320242281631021</v>
+        <v>0.1163061478557843</v>
       </c>
       <c r="CA3" t="n">
         <v>-0</v>
@@ -1808,31 +1808,31 @@
         <v>0</v>
       </c>
       <c r="CC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="n">
         <v>-0</v>
       </c>
       <c r="CE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CF3" t="n">
         <v>0</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.01894025474399924</v>
+        <v>0.0128933329044956</v>
       </c>
       <c r="CH3" t="n">
-        <v>-0.0008720681587888977</v>
+        <v>0.03982295511466673</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0.0970636524279626</v>
+        <v>-0.05687784901807016</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1844,46 +1844,46 @@
         <v>0</v>
       </c>
       <c r="CO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP3" t="n">
-        <v>-0.003492794481246962</v>
+        <v>0.007624748930886199</v>
       </c>
       <c r="CQ3" t="n">
-        <v>-0.02115982449754519</v>
+        <v>0.0195721853728003</v>
       </c>
       <c r="CR3" t="n">
-        <v>-0.02373757270871685</v>
+        <v>-0.02036889001254339</v>
       </c>
       <c r="CS3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CT3" t="n">
         <v>-0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
         <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CX3" t="n">
         <v>-0</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.0244168598420817</v>
+        <v>0.009838914260993908</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.004767563638659294</v>
+        <v>0.01545115548546064</v>
       </c>
       <c r="DA3" t="n">
-        <v>-0.08992352107104465</v>
+        <v>-0.05372449956940085</v>
       </c>
       <c r="DB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC3" t="n">
         <v>0</v>
@@ -1895,49 +1895,49 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0.01984978673041322</v>
+        <v>0.01105232748184075</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0.02627699406989251</v>
+        <v>0.005510811927220676</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0.02077541640713792</v>
+        <v>-0.03278433676158635</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DQ3" t="n">
-        <v>-0.01503995111913278</v>
+        <v>-0.03853479961667265</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.07076097943013691</v>
+        <v>0.007674992816750729</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.01380463233941497</v>
+        <v>-0.01091995275749739</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
@@ -1949,79 +1949,79 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DY3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ3" t="n">
-        <v>-0.03230563932452513</v>
+        <v>0.08120184636135561</v>
       </c>
       <c r="EA3" t="n">
-        <v>-0.006141079327499638</v>
+        <v>0.009855910987848151</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0.051662033000376</v>
+        <v>-0.008954050741693942</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EF3" t="n">
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EH3" t="n">
         <v>0</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.0585366265569453</v>
+        <v>0.01399311152268383</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.0270182361087934</v>
+        <v>0.01459826005571352</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0.1086868860668046</v>
+        <v>0.009407515858568753</v>
       </c>
       <c r="EL3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM3" t="n">
         <v>-0</v>
       </c>
       <c r="EN3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO3" t="n">
         <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EQ3" t="n">
         <v>0</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.04672893403672061</v>
+        <v>0.03891989741246118</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.03172565915530302</v>
+        <v>0.03684929380532022</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0.07087105212491739</v>
+        <v>-0.02046438880633091</v>
       </c>
       <c r="EU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
@@ -2036,19 +2036,19 @@
         <v>0</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.01557261574551646</v>
+        <v>0.03170712377934003</v>
       </c>
       <c r="FB3" t="n">
-        <v>-0.01728727679270572</v>
+        <v>0.03687966710438468</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0.08674334406668699</v>
+        <v>-0.06505811001441722</v>
       </c>
       <c r="FD3" t="n">
         <v>-0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,31 +2057,31 @@
         <v>-0</v>
       </c>
       <c r="FH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FI3" t="n">
         <v>-0</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0.009839159865455702</v>
+        <v>-0.0006403162772590347</v>
       </c>
       <c r="FK3" t="n">
-        <v>-0.02811539912733575</v>
+        <v>0.01626806815754927</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.0003142644878452895</v>
+        <v>0.08987408227748944</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>-0</v>
       </c>
       <c r="FO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ3" t="n">
         <v>0</v>
@@ -2090,16 +2090,16 @@
         <v>0</v>
       </c>
       <c r="FS3" t="n">
-        <v>-0.01925484836449415</v>
+        <v>-0.02411191596255999</v>
       </c>
       <c r="FT3" t="n">
-        <v>-0.1268052952161465</v>
+        <v>-0.1757143572496737</v>
       </c>
       <c r="FU3" t="n">
-        <v>-0.03847016567433773</v>
+        <v>-0.0005961277921540404</v>
       </c>
       <c r="FV3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW3" t="n">
         <v>0</v>
@@ -2108,28 +2108,28 @@
         <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
         <v>-0</v>
       </c>
       <c r="GA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.02741854847410577</v>
+        <v>0.06642839880392161</v>
       </c>
       <c r="GC3" t="n">
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.03229545231933784</v>
+        <v>0.02584246890680274</v>
       </c>
       <c r="GE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
         <v>-0</v>
